--- a/src/database/temp_outputs/all_states_surgery_npi_test.xlsx
+++ b/src/database/temp_outputs/all_states_surgery_npi_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC349223-90EF-415A-A3F8-39C3875C331E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFD06EA-ECC6-481D-BAE7-C5F5AFC0E727}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{8945120D-BF39-4DB2-BA30-B13791FF4541}"/>
   </bookViews>

--- a/src/database/temp_outputs/all_states_surgery_npi_test.xlsx
+++ b/src/database/temp_outputs/all_states_surgery_npi_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\temp_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFD06EA-ECC6-481D-BAE7-C5F5AFC0E727}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F60214E-E5CD-467A-AD4F-DE41EA1DDB9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{8945120D-BF39-4DB2-BA30-B13791FF4541}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9726" uniqueCount="3657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9738" uniqueCount="3664">
   <si>
     <t>Enrollment ID</t>
   </si>
@@ -10997,6 +10997,27 @@
   </si>
   <si>
     <t>I20050926000163</t>
+  </si>
+  <si>
+    <t>I20031124000326</t>
+  </si>
+  <si>
+    <t>Dunn</t>
+  </si>
+  <si>
+    <t>Family Practice</t>
+  </si>
+  <si>
+    <t>I20031104000582</t>
+  </si>
+  <si>
+    <t>Abt</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>General Practice</t>
   </si>
 </sst>
 </file>
@@ -11502,6 +11523,64 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3657</v>
+      </c>
+      <c r="B6">
+        <v>1083678858</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3658</v>
+      </c>
+      <c r="F6" t="s">
+        <v>613</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>3659</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3660</v>
+      </c>
+      <c r="B7">
+        <v>1184693400</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3661</v>
+      </c>
+      <c r="F7" t="s">
+        <v>3662</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>3663</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+    </row>
     <row r="129" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J129" s="1"/>
     </row>
